--- a/Rapid Cortex Internal Docs/Sales_Marketing/RC_Pricing_Master_Guide_v4.xlsx
+++ b/Rapid Cortex Internal Docs/Sales_Marketing/RC_Pricing_Master_Guide_v4.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Mac Mini/Coding Projects/Hibernation/WebApp/Rapid Cortex/Rapid Cortex Internal Docs/Sales_Marketing/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Mac Mini/Coding Projects/Hibernation/WebApp/NexCort iQ/NexCort iQ Internal Docs/Sales_Marketing/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACFCAB18-39A5-4C42-B2D1-F99528E3C346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -66,7 +66,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2215" uniqueCount="1284">
   <si>
-    <t>RAPID CORTEX</t>
+    <t>NEXCORT IQ</t>
   </si>
   <si>
     <t>INTERNAL PRICING GUIDE — CONFIDENTIAL</t>
@@ -240,13 +240,13 @@
     <t>23. Verticals Overview  —  All 5 product verticals — side-by-side comparison</t>
   </si>
   <si>
-    <t>24. Feature Add-Ons  —  QR &amp; NFC Codes · Agency Share · Rapid Cortex Connect</t>
-  </si>
-  <si>
-    <t>RAPID CORTEX — INTERNAL PRICING GUIDE</t>
-  </si>
-  <si>
-    <t>RAPID CORTEX ESSENTIAL</t>
+    <t>24. Feature Add-Ons  —  QR &amp; NFC Codes · Agency Share · NexCort iQ Connect</t>
+  </si>
+  <si>
+    <t>NEXCORT IQ — INTERNAL PRICING GUIDE</t>
+  </si>
+  <si>
+    <t>NEXCORT IQ ESSENTIAL</t>
   </si>
   <si>
     <t>Small municipalities · Single-site PSAPs · Pilot deployments · Up to 10 dispatcher seats</t>
@@ -528,7 +528,7 @@
     <t>⚠  INTERNAL USE ONLY — Public-facing: "Tailored deployment · Custom quote · Contact sales"</t>
   </si>
   <si>
-    <t>RAPID CORTEX PROFESSIONAL</t>
+    <t>NEXCORT IQ PROFESSIONAL</t>
   </si>
   <si>
     <t>Growing counties &amp; cities · Full features · Translation · QA · Analytics · Up to 25 dispatcher seats</t>
@@ -693,7 +693,7 @@
     <t>⚠  INTERNAL USE ONLY</t>
   </si>
   <si>
-    <t>RAPID CORTEX COMMAND</t>
+    <t>NEXCORT IQ COMMAND</t>
   </si>
   <si>
     <t>Large agencies · Regional command environments · Major incident coordination · Up to 75 dispatcher seats</t>
@@ -819,7 +819,7 @@
     <t xml:space="preserve">    Best for proving value during high-complexity incidents and cross-team response.</t>
   </si>
   <si>
-    <t xml:space="preserve">    Positions Rapid Cortex as a command and coordination platform, not just a dispatcher tool.</t>
+    <t xml:space="preserve">    Positions NexCort iQ as a command and coordination platform, not just a dispatcher tool.</t>
   </si>
   <si>
     <t xml:space="preserve">    Emphasize: war rooms, runbooks, and command dashboards for supervisors and leadership.</t>
@@ -978,7 +978,7 @@
     <t xml:space="preserve">  SALES POSITIONING — Enterprise / Statewide</t>
   </si>
   <si>
-    <t xml:space="preserve">    Best sales angle: Rapid Cortex becomes a long-term public safety modernization platform.</t>
+    <t xml:space="preserve">    Best sales angle: NexCort iQ becomes a long-term public safety modernization platform.</t>
   </si>
   <si>
     <t xml:space="preserve">    Strong fit for grant-funded programs, large procurements, and regional emergency management transformation.</t>
@@ -993,7 +993,7 @@
     <t>CAD INTEGRATION ADD-ONS</t>
   </si>
   <si>
-    <t>One-time fees · Complexity-tiered · Rapid Cortex enhances CAD — it does not replace it</t>
+    <t>One-time fees · Complexity-tiered · NexCort iQ enhances CAD — it does not replace it</t>
   </si>
   <si>
     <t xml:space="preserve">  DISCOVERY &amp; PLANNING</t>
@@ -1446,7 +1446,7 @@
     <t xml:space="preserve">  SALES POSITIONING — Onsite Services</t>
   </si>
   <si>
-    <t xml:space="preserve">    Reduces rollout risk by putting Rapid Cortex experts with agency staff.</t>
+    <t xml:space="preserve">    Reduces rollout risk by putting NexCort iQ experts with agency staff.</t>
   </si>
   <si>
     <t xml:space="preserve">    Especially valuable for complex workflows, multiple stakeholders, or limited internal IT.</t>
@@ -1515,7 +1515,7 @@
     <t xml:space="preserve">    Training protects the agency from workflow confusion and reduces support burden.</t>
   </si>
   <si>
-    <t xml:space="preserve">    Helps teams understand what Rapid Cortex does vs. CAD, CPE, SOPs, and AI decision support.</t>
+    <t xml:space="preserve">    Helps teams understand what NexCort iQ does vs. CAD, CPE, SOPs, and AI decision support.</t>
   </si>
   <si>
     <t xml:space="preserve">    Train-the-Trainer is high-margin and creates internal champions — recommend for Command+.</t>
@@ -1641,7 +1641,7 @@
     <t xml:space="preserve">    Mission-Critical support recommended for Command, Enterprise, and any agency in active production.</t>
   </si>
   <si>
-    <t xml:space="preserve">    Dedicated support turns Rapid Cortex from a software vendor into an operational partner.</t>
+    <t xml:space="preserve">    Dedicated support turns NexCort iQ from a software vendor into an operational partner.</t>
   </si>
   <si>
     <t xml:space="preserve">    Priority support is included in Professional — be clear that Mission-Critical is an upgrade.</t>
@@ -1782,7 +1782,7 @@
     <t xml:space="preserve">  SALES POSITIONING — Storage &amp; Overages</t>
   </si>
   <si>
-    <t xml:space="preserve">    Overages protect both the agency and Rapid Cortex by allowing flexible usage without forcing an immediate plan change.</t>
+    <t xml:space="preserve">    Overages protect both the agency and NexCort iQ by allowing flexible usage without forcing an immediate plan change.</t>
   </si>
   <si>
     <t xml:space="preserve">    Useful during storms, major incidents, seasonal spikes, or large-scale emergencies.</t>
@@ -1854,7 +1854,7 @@
     <t xml:space="preserve">  SALES POSITIONING — Small City Pilot</t>
   </si>
   <si>
-    <t xml:space="preserve">    Smaller municipalities that want to evaluate Rapid Cortex without a full production commitment.</t>
+    <t xml:space="preserve">    Smaller municipalities that want to evaluate NexCort iQ without a full production commitment.</t>
   </si>
   <si>
     <t xml:space="preserve">    Usually includes Essential-level access, setup, onboarding, training, and CAD discovery.</t>
@@ -1884,7 +1884,7 @@
     <t xml:space="preserve">    May include Command-level tools, war rooms, onsite support, and expanded training.</t>
   </si>
   <si>
-    <t xml:space="preserve">    Sales angle: proves Rapid Cortex as a command and coordination platform.</t>
+    <t xml:space="preserve">    Sales angle: proves NexCort iQ as a command and coordination platform.</t>
   </si>
   <si>
     <t xml:space="preserve">  SALES POSITIONING — Enterprise / Statewide Program</t>
@@ -2157,7 +2157,7 @@
     <t>REFS</t>
   </si>
   <si>
-    <t>Apps on Demand LLC  d/b/a  Rapid Cortex  |  Intelligence at the Speed of Response</t>
+    <t>Apps on Demand LLC  d/b/a  NexCort iQ  |  Intelligence at the Speed of Response</t>
   </si>
   <si>
     <t xml:space="preserve">  QUOTE DETAILS</t>
@@ -2235,10 +2235,10 @@
     <t>• All fees are in USD. Government tax exemption honored upon receipt of certificate.</t>
   </si>
   <si>
-    <t>• To proceed: return signed Pilot Scope Agreement or contact your Rapid Cortex representative.</t>
-  </si>
-  <si>
-    <t>Rapid Cortex  |  Apps on Demand LLC  |  intelligence@rapidcortex.us  |  rapidcortex.us  |  CONFIDENTIAL — NOT FOR DISTRIBUTION</t>
+    <t>• To proceed: return signed Pilot Scope Agreement or contact your NexCort iQ representative.</t>
+  </si>
+  <si>
+    <t>NexCort iQ  |  Apps on Demand LLC  |  intelligence@rapidcortex.us  |  rapidcortex.us  |  CONFIDENTIAL — NOT FOR DISTRIBUTION</t>
   </si>
   <si>
     <t>DISCOUNTING RULES</t>
@@ -2373,7 +2373,7 @@
     <t>RULE: Discounts reward commitment, scale, and strategic value — not just pressure to close.</t>
   </si>
   <si>
-    <t>RAPID CORTEX CAMPUS</t>
+    <t>NEXCORT IQ CAMPUS</t>
   </si>
   <si>
     <t>Universities · Colleges · K-12 · Campus safety reporting · QR/NFC · Anonymous &amp; identified reporting · Clery documentation</t>
@@ -2676,7 +2676,7 @@
     <t>Additional zones beyond standard config</t>
   </si>
   <si>
-    <t>Rapid Cortex Connect — Camera Integ.</t>
+    <t>NexCort iQ Connect — Camera Integ.</t>
   </si>
   <si>
     <t>$5,000</t>
@@ -2739,7 +2739,7 @@
     <t>⚠  INTERNAL USE ONLY — Do not share with agencies or prospects without Sales Director approval.</t>
   </si>
   <si>
-    <t>RAPID CORTEX VENUE</t>
+    <t>NEXCORT IQ VENUE</t>
   </si>
   <si>
     <t>Stadiums · Arenas · Convention centers · Concert venues · Fan-to-security communication · QR/NFC · Zone-based reporting</t>
@@ -2937,13 +2937,13 @@
     <t>Per event · plus travel</t>
   </si>
   <si>
-    <t xml:space="preserve">  SALES POSITIONING: 'Most venue security focuses on cameras and access control. Rapid Cortex Venue is the only platform built around frictionless fan-to-security communication.' QR + NFC on seat backs and concourse signs means any fan can report in 10 seconds without an app.</t>
+    <t xml:space="preserve">  SALES POSITIONING: 'Most venue security focuses on cameras and access control. NexCort iQ Venue is the only platform built around frictionless fan-to-security communication.' QR + NFC on seat backs and concourse signs means any fan can report in 10 seconds without an app.</t>
   </si>
   <si>
     <t>⚠  INTERNAL USE ONLY — Do not share without Sales Director approval.</t>
   </si>
   <si>
-    <t>RAPID CORTEX HOSPITAL</t>
+    <t>NEXCORT IQ HOSPITAL</t>
   </si>
   <si>
     <t>Hospitals · Health systems · EMS coordination · Pre-alert intake · MCI support · Patient tracking</t>
@@ -3090,7 +3090,7 @@
     <t>Per month</t>
   </si>
   <si>
-    <t>RAPID CORTEX TRANSIT</t>
+    <t>NEXCORT IQ TRANSIT</t>
   </si>
   <si>
     <t>Transit authorities · Bus &amp; rail · Passenger safety reporting · Vehicle/station incidents · Two-way chat · QR/NFC</t>
@@ -3234,7 +3234,7 @@
     <t>Passenger ↔ security translation</t>
   </si>
   <si>
-    <t>RAPID CORTEX — PRODUCT VERTICALS OVERVIEW</t>
+    <t>NEXCORT IQ — PRODUCT VERTICALS OVERVIEW</t>
   </si>
   <si>
     <t>RC 911 · RC Campus · RC Venue · RC Hospital · RC Transit — side-by-side comparison</t>
@@ -3360,7 +3360,7 @@
     <t>All verticals — Cortex AI</t>
   </si>
   <si>
-    <t>Rapid Cortex Connect (cameras)</t>
+    <t>NexCort iQ Connect (cameras)</t>
   </si>
   <si>
     <t>ONVIF/RTSP/WebRTC</t>
@@ -3432,7 +3432,7 @@
     <t>FEATURE ADD-ONS</t>
   </si>
   <si>
-    <t>QR &amp; NFC Code Management · Agency Share · Rapid Cortex Connect · SMS Location Acquisition</t>
+    <t>QR &amp; NFC Code Management · Agency Share · NexCort iQ Connect · SMS Location Acquisition</t>
   </si>
   <si>
     <t xml:space="preserve">  QR &amp; NFC CODE MANAGEMENT</t>
@@ -3549,7 +3549,7 @@
     <t xml:space="preserve">  AGENCY SHARE — FEATURE (not a separate product)</t>
   </si>
   <si>
-    <t xml:space="preserve">  Agency Share enables controlled, consent-based incident awareness between partner agencies. It is a feature of the Rapid Cortex platform — not a standalone product. Agencies must establish a partnership agreement before data sharing is enabled.</t>
+    <t xml:space="preserve">  Agency Share enables controlled, consent-based incident awareness between partner agencies. It is a feature of the NexCort iQ platform — not a standalone product. Agencies must establish a partnership agreement before data sharing is enabled.</t>
   </si>
   <si>
     <t>Per agency, per month</t>
@@ -3609,7 +3609,7 @@
     <t>Admin UI</t>
   </si>
   <si>
-    <t>Agency Partnership tab in RC Admin</t>
+    <t>Agency Partnership tab in NC Admin</t>
   </si>
   <si>
     <t>Feature toggle — locked until partnership exists</t>
@@ -3624,10 +3624,10 @@
     <t>CJIS-aware · us-east-1 only</t>
   </si>
   <si>
-    <t xml:space="preserve">  RAPID CORTEX CONNECT — CAMERA INTEGRATION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Rapid Cortex Connect integrates existing cameras into the incident console. Open standards (ONVIF, RTSP, WebRTC) are available now. Vendor-specific integrations (Ring, Nest, Verkada, Eagle Eye) are Phase 3.</t>
+    <t xml:space="preserve">  NEXCORT IQ CONNECT — CAMERA INTEGRATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  NexCort iQ Connect integrates existing cameras into the incident console. Open standards (ONVIF, RTSP, WebRTC) are available now. Vendor-specific integrations (Ring, Nest, Verkada, Eagle Eye) are Phase 3.</t>
   </si>
   <si>
     <t>Tier / Item</t>
